--- a/AAII_Financials/Quarterly/AXAHY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AXAHY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="92">
   <si>
     <t>AXAHY</t>
   </si>
@@ -656,170 +656,176 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="39" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -865,80 +871,86 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T8" s="3">
         <v>46658800</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V8" s="3">
         <v>66747000</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X8" s="3">
         <v>64718900</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="3">
         <v>60717700</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="3">
         <v>57239000</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="3">
         <v>69144500</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="3">
         <v>87884100</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="3">
         <v>59560200</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>62945000</v>
       </c>
-      <c r="AI8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL8" s="3">
         <v>74261200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>27278900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>74842300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>37138200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>76189700</v>
       </c>
-      <c r="AO8" s="3" t="s">
+      <c r="AQ8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -984,80 +996,86 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T9" s="3">
         <v>6876800</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V9" s="3">
         <v>7601700</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X9" s="3">
         <v>6391400</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z9" s="3">
         <v>6250700</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB9" s="3">
         <v>6945800</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD9" s="3">
         <v>7444600</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF9" s="3">
         <v>7939500</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="3">
         <v>7292600</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ9" s="3">
         <v>6045600</v>
       </c>
-      <c r="AI9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL9" s="3">
         <v>6122700</v>
       </c>
-      <c r="AK9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN9" s="3">
         <v>5991400</v>
       </c>
-      <c r="AM9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP9" s="3">
         <v>7053400</v>
       </c>
-      <c r="AO9" s="3" t="s">
+      <c r="AQ9" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1103,80 +1121,86 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T10" s="3">
         <v>39782000</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V10" s="3">
         <v>59145200</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X10" s="3">
         <v>58327500</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="3">
         <v>54467000</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB10" s="3">
         <v>50293100</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD10" s="3">
         <v>61700000</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF10" s="3">
         <v>79944600</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="3">
         <v>52267600</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ10" s="3">
         <v>56899500</v>
       </c>
-      <c r="AI10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL10" s="3">
         <v>68138500</v>
       </c>
-      <c r="AK10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN10" s="3">
         <v>68850900</v>
       </c>
-      <c r="AM10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP10" s="3">
         <v>69136200</v>
       </c>
-      <c r="AO10" s="3" t="s">
+      <c r="AQ10" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1218,8 +1242,10 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1337,8 +1363,14 @@
       <c r="AO12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1456,8 +1488,14 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1503,80 +1541,86 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3">
         <v>1019500</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V14" s="3">
         <v>673200</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14" s="3">
         <v>219000</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="3">
         <v>364100</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="3">
         <v>910900</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD14" s="3">
         <v>944400</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF14" s="3">
         <v>200000</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH14" s="3">
         <v>8676600</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>413900</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL14" s="3">
         <v>265900</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN14" s="3">
         <v>198600</v>
       </c>
-      <c r="AM14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP14" s="3">
         <v>535300</v>
       </c>
-      <c r="AO14" s="3" t="s">
+      <c r="AQ14" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1619,11 +1663,11 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1694,8 +1738,14 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1734,8 +1784,10 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1781,80 +1833,86 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T17" s="3">
         <v>41027900</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V17" s="3">
         <v>62189400</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X17" s="3">
         <v>59100900</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z17" s="3">
         <v>58138400</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB17" s="3">
         <v>54223700</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD17" s="3">
         <v>66272700</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF17" s="3">
         <v>83907900</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH17" s="3">
         <v>62393200</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>58333400</v>
       </c>
-      <c r="AI17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL17" s="3">
         <v>70413800</v>
       </c>
-      <c r="AK17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN17" s="3">
         <v>70011100</v>
       </c>
-      <c r="AM17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP17" s="3">
         <v>71616500</v>
       </c>
-      <c r="AO17" s="3" t="s">
+      <c r="AQ17" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1900,80 +1958,86 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3">
         <v>5630900</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V18" s="3">
         <v>4557600</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X18" s="3">
         <v>5618000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z18" s="3">
         <v>2579300</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB18" s="3">
         <v>3015300</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD18" s="3">
         <v>2871800</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="3">
         <v>3976200</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-2833000</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>4611600</v>
       </c>
-      <c r="AI18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL18" s="3">
         <v>3847300</v>
       </c>
-      <c r="AK18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN18" s="3">
         <v>4831300</v>
       </c>
-      <c r="AM18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP18" s="3">
         <v>4573200</v>
       </c>
-      <c r="AO18" s="3" t="s">
+      <c r="AQ18" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2015,8 +2079,10 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2062,80 +2128,86 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="3">
         <v>-99000</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="3">
         <v>108400</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X20" s="3">
         <v>46600</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z20" s="3">
         <v>209500</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB20" s="3">
         <v>207300</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD20" s="3">
         <v>283700</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="3">
         <v>307000</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH20" s="3">
         <v>186900</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>141600</v>
       </c>
-      <c r="AI20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL20" s="3">
         <v>179500</v>
       </c>
-      <c r="AK20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN20" s="3">
         <v>118900</v>
       </c>
-      <c r="AM20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP20" s="3">
         <v>146700</v>
       </c>
-      <c r="AO20" s="3" t="s">
+      <c r="AQ20" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2187,74 +2259,80 @@
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>5609100</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="3">
         <v>3961700</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="3">
         <v>3854800</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="3">
         <v>5197300</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3">
         <v>-1864300</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>4959700</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL21" s="3">
         <v>4249000</v>
       </c>
-      <c r="AK21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN21" s="3">
         <v>5211600</v>
       </c>
-      <c r="AM21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP21" s="3">
         <v>5062600</v>
       </c>
-      <c r="AO21" s="3" t="s">
+      <c r="AQ21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2300,80 +2378,86 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T22" s="3">
         <v>282900</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V22" s="3">
         <v>236300</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X22" s="3">
         <v>258200</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z22" s="3">
         <v>243400</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB22" s="3">
         <v>691600</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD22" s="3">
         <v>335000</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF22" s="3">
         <v>509400</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH22" s="3">
         <v>454200</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>195400</v>
       </c>
-      <c r="AI22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL22" s="3">
         <v>148100</v>
       </c>
-      <c r="AK22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN22" s="3">
         <v>205300</v>
       </c>
-      <c r="AM22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP22" s="3">
         <v>78600</v>
       </c>
-      <c r="AO22" s="3" t="s">
+      <c r="AQ22" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2419,80 +2503,86 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T23" s="3">
         <v>5249000</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V23" s="3">
         <v>4429600</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X23" s="3">
         <v>5406400</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z23" s="3">
         <v>2545400</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB23" s="3">
         <v>2530900</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD23" s="3">
         <v>2820500</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF23" s="3">
         <v>3773900</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH23" s="3">
         <v>-3100400</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>4557800</v>
       </c>
-      <c r="AI23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL23" s="3">
         <v>3878700</v>
       </c>
-      <c r="AK23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN23" s="3">
         <v>4744900</v>
       </c>
-      <c r="AM23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP23" s="3">
         <v>4641200</v>
       </c>
-      <c r="AO23" s="3" t="s">
+      <c r="AQ23" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2538,80 +2628,86 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T24" s="3">
         <v>978200</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V24" s="3">
         <v>754500</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X24" s="3">
         <v>1050600</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z24" s="3">
         <v>729100</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB24" s="3">
         <v>883600</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD24" s="3">
         <v>914100</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF24" s="3">
         <v>748200</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH24" s="3">
         <v>803200</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>872900</v>
       </c>
-      <c r="AI24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL24" s="3">
         <v>329900</v>
       </c>
-      <c r="AK24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN24" s="3">
         <v>885300</v>
       </c>
-      <c r="AM24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP24" s="3">
         <v>1317000</v>
       </c>
-      <c r="AO24" s="3" t="s">
+      <c r="AQ24" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2729,8 +2825,14 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2776,80 +2878,86 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T26" s="3">
         <v>4270800</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V26" s="3">
         <v>3675100</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X26" s="3">
         <v>4355800</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z26" s="3">
         <v>1816300</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB26" s="3">
         <v>1647300</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD26" s="3">
         <v>1906400</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF26" s="3">
         <v>3025700</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH26" s="3">
         <v>-3903600</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>3684900</v>
       </c>
-      <c r="AI26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL26" s="3">
         <v>3548900</v>
       </c>
-      <c r="AK26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN26" s="3">
         <v>3859600</v>
       </c>
-      <c r="AM26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP26" s="3">
         <v>3324200</v>
       </c>
-      <c r="AO26" s="3" t="s">
+      <c r="AQ26" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2895,80 +3003,86 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T27" s="3">
         <v>4090200</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V27" s="3">
         <v>3469100</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X27" s="3">
         <v>4126200</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z27" s="3">
         <v>1644700</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB27" s="3">
         <v>1460700</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD27" s="3">
         <v>1670600</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF27" s="3">
         <v>2584600</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH27" s="3">
         <v>-851700</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>3322500</v>
       </c>
-      <c r="AI27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL27" s="3">
         <v>3173000</v>
       </c>
-      <c r="AK27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN27" s="3">
         <v>3536500</v>
       </c>
-      <c r="AM27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP27" s="3">
         <v>2969700</v>
       </c>
-      <c r="AO27" s="3" t="s">
+      <c r="AQ27" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3086,8 +3200,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3130,11 +3250,11 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -3145,68 +3265,74 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>4</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-28000</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-95800</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-381000</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL29" s="3">
         <v>1100</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN29" s="3">
         <v>-1100</v>
       </c>
-      <c r="AM29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP29" s="3">
         <v>-41100</v>
       </c>
-      <c r="AO29" s="3" t="s">
+      <c r="AQ29" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3324,8 +3450,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3443,8 +3575,14 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3490,80 +3628,86 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3">
         <v>99000</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V32" s="3">
         <v>-108400</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X32" s="3">
         <v>-46600</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-209500</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-207300</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-283700</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-307000</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-186900</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-141600</v>
       </c>
-      <c r="AI32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL32" s="3">
         <v>-179500</v>
       </c>
-      <c r="AK32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN32" s="3">
         <v>-118900</v>
       </c>
-      <c r="AM32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP32" s="3">
         <v>-146700</v>
       </c>
-      <c r="AO32" s="3" t="s">
+      <c r="AQ32" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3609,80 +3753,86 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T33" s="3">
         <v>4090200</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V33" s="3">
         <v>3469100</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X33" s="3">
         <v>4126200</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z33" s="3">
         <v>1644700</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB33" s="3">
         <v>1460700</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD33" s="3">
         <v>1642500</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF33" s="3">
         <v>2584600</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH33" s="3">
         <v>-947500</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>2941500</v>
       </c>
-      <c r="AI33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL33" s="3">
         <v>3174100</v>
       </c>
-      <c r="AK33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN33" s="3">
         <v>3535400</v>
       </c>
-      <c r="AM33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP33" s="3">
         <v>2928700</v>
       </c>
-      <c r="AO33" s="3" t="s">
+      <c r="AQ33" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3800,8 +3950,14 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3847,204 +4003,216 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T35" s="3">
         <v>4090200</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V35" s="3">
         <v>3469100</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X35" s="3">
         <v>4126200</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z35" s="3">
         <v>1644700</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB35" s="3">
         <v>1460700</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD35" s="3">
         <v>1642500</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF35" s="3">
         <v>2584600</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH35" s="3">
         <v>-947500</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>2941500</v>
       </c>
-      <c r="AI35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL35" s="3">
         <v>3174100</v>
       </c>
-      <c r="AK35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN35" s="3">
         <v>3535400</v>
       </c>
-      <c r="AM35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP35" s="3">
         <v>2928700</v>
       </c>
-      <c r="AO35" s="3" t="s">
+      <c r="AQ35" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4086,8 +4254,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4129,56 +4299,58 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21156200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>21351300</v>
+      </c>
+      <c r="F41" s="3">
         <v>26123000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>26104700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>26371100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>24270400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>19658300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>21177800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>23654800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>23818100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>28057900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>26867100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>29234700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>29095000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>27965200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>4</v>
       </c>
@@ -4206,98 +4378,104 @@
       <c r="AA41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AB41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD41" s="3">
         <v>25622300</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF41" s="3">
         <v>27840700</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH41" s="3">
         <v>37059100</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>44189000</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL41" s="3">
         <v>26813300</v>
       </c>
-      <c r="AK41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN41" s="3">
         <v>29988500</v>
       </c>
-      <c r="AM41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP41" s="3">
         <v>30887600</v>
       </c>
-      <c r="AO41" s="3" t="s">
+      <c r="AQ41" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>54956000</v>
+        <v>92931600</v>
       </c>
       <c r="E42" s="3">
-        <v>54917300</v>
+        <v>93788800</v>
       </c>
       <c r="F42" s="3">
+        <v>59248600</v>
+      </c>
+      <c r="G42" s="3">
+        <v>59206900</v>
+      </c>
+      <c r="H42" s="3">
         <v>57398700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>52826400</v>
       </c>
-      <c r="H42" s="3">
-        <v>50579800</v>
-      </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
+        <v>55464300</v>
+      </c>
+      <c r="K42" s="3">
         <v>54489200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>55991600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>56378300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>54979600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>52646100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>48981400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>48747300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>16943500</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
       <c r="S42" s="3">
         <v>0</v>
       </c>
@@ -4367,56 +4545,62 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14246500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>14378000</v>
+      </c>
+      <c r="F43" s="3">
         <v>8771900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>8765700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>12196100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>11224600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>7445900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>8021400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>13676200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>13770600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>8964300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>8583800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>13298000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>13234500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>8296500</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>4</v>
       </c>
@@ -4444,50 +4628,56 @@
       <c r="AA43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AB43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD43" s="3">
         <v>46101000</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF43" s="3">
         <v>50055800</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH43" s="3">
         <v>49621500</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>36964200</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL43" s="3">
         <v>33930100</v>
       </c>
-      <c r="AK43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN43" s="3">
         <v>35932900</v>
       </c>
-      <c r="AM43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP43" s="3">
         <v>40889700</v>
       </c>
-      <c r="AO43" s="3" t="s">
+      <c r="AQ43" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4530,11 +4720,11 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -4605,56 +4795,62 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>37708100</v>
+        <v>36694800</v>
       </c>
       <c r="E45" s="3">
-        <v>37681600</v>
+        <v>37033300</v>
       </c>
       <c r="F45" s="3">
+        <v>33415500</v>
+      </c>
+      <c r="G45" s="3">
+        <v>33392000</v>
+      </c>
+      <c r="H45" s="3">
         <v>42676500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>39276900</v>
       </c>
-      <c r="H45" s="3">
-        <v>40887300</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
+        <v>36002700</v>
+      </c>
+      <c r="K45" s="3">
         <v>44047500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>37293500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>37551000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>42566600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>40759900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>55901700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>55634500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>60878500</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
       <c r="S45" s="3">
         <v>0</v>
       </c>
@@ -4724,56 +4920,62 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>165029100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>166551400</v>
+      </c>
+      <c r="F46" s="3">
         <v>127559000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>127469200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>138642400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>127598400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>118571300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>127735900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>130616100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>131518000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>134568400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>128856900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>147415900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>146711200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>114083600</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
       <c r="S46" s="3">
         <v>0</v>
       </c>
@@ -4843,56 +5045,62 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>363605600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>366959500</v>
+      </c>
+      <c r="F47" s="3">
         <v>403320400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>403036500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>410900800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>378169000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>371256900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>399952000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>365395900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>367918900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>383660900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>367377200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>359607000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>357887900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>387322900</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>4</v>
       </c>
@@ -4920,98 +5128,104 @@
       <c r="AA47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AB47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD47" s="3">
         <v>607683600</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF47" s="3">
         <v>626980000</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH47" s="3">
         <v>675838100</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>583420100</v>
       </c>
-      <c r="AI47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL47" s="3">
         <v>621847200</v>
       </c>
-      <c r="AK47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN47" s="3">
         <v>629155900</v>
       </c>
-      <c r="AM47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP47" s="3">
         <v>668663200</v>
       </c>
-      <c r="AO47" s="3" t="s">
+      <c r="AQ47" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2446000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2468600</v>
+      </c>
+      <c r="F48" s="3">
         <v>2520800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2519100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2540200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2337900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2290100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2467100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2541500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2559100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2315700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2217400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2346100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2334900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2384300</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
@@ -5039,98 +5253,104 @@
       <c r="AA48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD48" s="3">
         <v>30554600</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF48" s="3">
         <v>28690000</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH48" s="3">
         <v>26660200</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>23030600</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL48" s="3">
         <v>27467400</v>
       </c>
-      <c r="AK48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN48" s="3">
         <v>26979400</v>
       </c>
-      <c r="AM48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP48" s="3">
         <v>26870900</v>
       </c>
-      <c r="AO48" s="3" t="s">
+      <c r="AQ48" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>25812900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>26051000</v>
+      </c>
+      <c r="F49" s="3">
         <v>25625200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>25607200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>25118000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>23117200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>22941300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>24714500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>24455200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>24624000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>24402600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>23366900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>23929000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>23814600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>23534300</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>4</v>
       </c>
@@ -5158,50 +5378,56 @@
       <c r="AA49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AB49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD49" s="3">
         <v>26439500</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF49" s="3">
         <v>25403200</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH49" s="3">
         <v>25800200</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>20690700</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL49" s="3">
         <v>20825300</v>
       </c>
-      <c r="AK49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN49" s="3">
         <v>21486100</v>
       </c>
-      <c r="AM49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP49" s="3">
         <v>23418700</v>
       </c>
-      <c r="AO49" s="3" t="s">
+      <c r="AQ49" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5319,8 +5545,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5438,56 +5670,62 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>153420500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>154835700</v>
+      </c>
+      <c r="F52" s="3">
         <v>151822200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>151715400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>145598400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>134000200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>128981300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>138950500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>127056700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>127934000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>130190100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>124664500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>123857000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>123264900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>117291900</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>4</v>
       </c>
@@ -5515,50 +5753,56 @@
       <c r="AA52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD52" s="3">
         <v>42311600</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF52" s="3">
         <v>11622800</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH52" s="3">
         <v>32292000</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>34771500</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL52" s="3">
         <v>6570400</v>
       </c>
-      <c r="AK52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN52" s="3">
         <v>2874500</v>
       </c>
-      <c r="AM52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP52" s="3">
         <v>2954500</v>
       </c>
-      <c r="AO52" s="3" t="s">
+      <c r="AQ52" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5676,56 +5920,62 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>743395400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>750252500</v>
+      </c>
+      <c r="F54" s="3">
         <v>746200500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>745675200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>758156200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>697762600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>676842300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>729156800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>684593400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>689320300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>712263700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>682033200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>693859200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>690542200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>682224000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>4</v>
       </c>
@@ -5753,50 +6003,56 @@
       <c r="AA54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AB54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD54" s="3">
         <v>911604800</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF54" s="3">
         <v>898192000</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH54" s="3">
         <v>1100919100</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ54" s="3">
         <v>982903200</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL54" s="3">
         <v>976274900</v>
       </c>
-      <c r="AK54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN54" s="3">
         <v>986956300</v>
       </c>
-      <c r="AM54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP54" s="3">
         <v>1047957600</v>
       </c>
-      <c r="AO54" s="3" t="s">
+      <c r="AQ54" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5838,8 +6094,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5881,56 +6139,58 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8200</v>
+        <v>8000</v>
       </c>
       <c r="E57" s="3">
-        <v>8200</v>
+        <v>8100</v>
       </c>
       <c r="F57" s="3">
         <v>8200</v>
       </c>
       <c r="G57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="H57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="I57" s="3">
         <v>7600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>6700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>8600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>8600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>8800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>8500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>7600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>7600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>5300</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
@@ -6000,56 +6260,62 @@
       <c r="AO57" s="3">
         <v>0</v>
       </c>
+      <c r="AP57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>44793900</v>
+        <v>683200</v>
       </c>
       <c r="E58" s="3">
-        <v>44762400</v>
+        <v>689500</v>
       </c>
       <c r="F58" s="3">
+        <v>48411400</v>
+      </c>
+      <c r="G58" s="3">
+        <v>48377300</v>
+      </c>
+      <c r="H58" s="3">
         <v>788000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>725200</v>
       </c>
-      <c r="H58" s="3">
-        <v>35226200</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
+        <v>38642700</v>
+      </c>
+      <c r="K58" s="3">
         <v>37948900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>665400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>670000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>39207500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>37543400</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>42824600</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
@@ -6119,56 +6385,62 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>21231700</v>
+        <v>13621600</v>
       </c>
       <c r="E59" s="3">
-        <v>21216700</v>
+        <v>13747300</v>
       </c>
       <c r="F59" s="3">
+        <v>14332500</v>
+      </c>
+      <c r="G59" s="3">
+        <v>14322400</v>
+      </c>
+      <c r="H59" s="3">
         <v>15765100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>14509300</v>
       </c>
-      <c r="H59" s="3">
-        <v>22452600</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
+        <v>15730400</v>
+      </c>
+      <c r="K59" s="3">
         <v>24188000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>15911300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>16021100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>25271400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>24198800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>34066600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>33903700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>43947800</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>4</v>
       </c>
@@ -6196,98 +6468,104 @@
       <c r="AA59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD59" s="3">
         <v>230256400</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF59" s="3">
         <v>248559200</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH59" s="3">
         <v>361186700</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>339188700</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL59" s="3">
         <v>341091700</v>
       </c>
-      <c r="AK59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN59" s="3">
         <v>339035100</v>
       </c>
-      <c r="AM59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP59" s="3">
         <v>360436000</v>
       </c>
-      <c r="AO59" s="3" t="s">
+      <c r="AQ59" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>66177100</v>
+        <v>14312800</v>
       </c>
       <c r="E60" s="3">
-        <v>66130500</v>
+        <v>14444800</v>
       </c>
       <c r="F60" s="3">
+        <v>62895400</v>
+      </c>
+      <c r="G60" s="3">
+        <v>62851100</v>
+      </c>
+      <c r="H60" s="3">
         <v>16561400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>15242100</v>
       </c>
-      <c r="H60" s="3">
-        <v>57777200</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
+        <v>54471500</v>
+      </c>
+      <c r="K60" s="3">
         <v>62242900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>16585200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>16699800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>64580500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>61839500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>34074200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>33911300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>86879300</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
-      <c r="R60" s="3">
-        <v>0</v>
-      </c>
       <c r="S60" s="3">
         <v>0</v>
       </c>
@@ -6357,56 +6635,62 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>26056100</v>
+        <v>69131700</v>
       </c>
       <c r="E61" s="3">
-        <v>26037800</v>
+        <v>69769400</v>
       </c>
       <c r="F61" s="3">
+        <v>28704900</v>
+      </c>
+      <c r="G61" s="3">
+        <v>28684700</v>
+      </c>
+      <c r="H61" s="3">
         <v>76712900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>70602000</v>
       </c>
-      <c r="H61" s="3">
-        <v>29107600</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
+        <v>31972300</v>
+      </c>
+      <c r="K61" s="3">
         <v>31357300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>64456200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>64901300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>26605500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>25476300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>63867900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>63562600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>25207900</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -6435,97 +6719,103 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>22589400</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>20571700</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>27295400</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>21744800</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
         <v>16549400</v>
       </c>
-      <c r="AK61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="3">
         <v>12567400</v>
       </c>
-      <c r="AM61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP61" s="3">
         <v>14227800</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>585458500</v>
+        <v>599022000</v>
       </c>
       <c r="E62" s="3">
-        <v>585046300</v>
+        <v>604547400</v>
       </c>
       <c r="F62" s="3">
+        <v>586091300</v>
+      </c>
+      <c r="G62" s="3">
+        <v>585678800</v>
+      </c>
+      <c r="H62" s="3">
         <v>596186700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>548695400</v>
       </c>
-      <c r="H62" s="3">
-        <v>521780700</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
+        <v>522221800</v>
+      </c>
+      <c r="K62" s="3">
         <v>562110200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>538051000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>541766100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>548925600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>525627600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>533259800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>530710600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>504977000</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>4</v>
       </c>
@@ -6553,50 +6843,56 @@
       <c r="AA62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD62" s="3">
         <v>46929900</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF62" s="3">
         <v>14636800</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH62" s="3">
         <v>34705100</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>39270000</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL62" s="3">
         <v>11447700</v>
       </c>
-      <c r="AK62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN62" s="3">
         <v>8199500</v>
       </c>
-      <c r="AM62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP62" s="3">
         <v>8330500</v>
       </c>
-      <c r="AO62" s="3" t="s">
+      <c r="AQ62" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6714,8 +7010,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6833,8 +7135,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6952,56 +7260,62 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>684942300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>691260200</v>
+      </c>
+      <c r="F66" s="3">
         <v>683787700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>683306300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>691691100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>636592100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>614079100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>661542500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>621359700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>625650000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>645953400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>618537300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>633041500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>630015200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>622920800</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>4</v>
       </c>
@@ -7029,50 +7343,56 @@
       <c r="AA66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD66" s="3">
         <v>830006300</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF66" s="3">
         <v>819696700</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH66" s="3">
         <v>1027073000</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>910480300</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL66" s="3">
         <v>898172100</v>
       </c>
-      <c r="AK66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN66" s="3">
         <v>910709200</v>
       </c>
-      <c r="AM66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP66" s="3">
         <v>965090100</v>
       </c>
-      <c r="AO66" s="3" t="s">
+      <c r="AQ66" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7114,8 +7434,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7233,8 +7555,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7352,8 +7680,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7471,8 +7805,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7590,56 +7930,62 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>46446900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>46875400</v>
+      </c>
+      <c r="F72" s="3">
         <v>48622800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>48588500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>41786300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>38457600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>37771000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>40690400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>35077700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>35319900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>36634200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>35079400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>32842800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>32685800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>32172700</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>4</v>
       </c>
@@ -7667,50 +8013,56 @@
       <c r="AA72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD72" s="3">
         <v>30273300</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF72" s="3">
         <v>29495900</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH72" s="3">
         <v>31401300</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>11626700</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL72" s="3">
         <v>36005800</v>
       </c>
-      <c r="AK72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN72" s="3">
         <v>33463400</v>
       </c>
-      <c r="AM72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP72" s="3">
         <v>34574600</v>
       </c>
-      <c r="AO72" s="3" t="s">
+      <c r="AQ72" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7828,8 +8180,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7947,8 +8305,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8066,56 +8430,62 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51059100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>51530000</v>
+      </c>
+      <c r="F76" s="3">
         <v>55384500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>55345500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>53424500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>49168800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>51706200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>55702700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>50723200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>51073500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>54801600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>52475700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>50122300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>49882700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>49238000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>4</v>
       </c>
@@ -8143,50 +8513,56 @@
       <c r="AA76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AB76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD76" s="3">
         <v>81598500</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF76" s="3">
         <v>78495300</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH76" s="3">
         <v>73846100</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>72423000</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL76" s="3">
         <v>78102800</v>
       </c>
-      <c r="AK76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN76" s="3">
         <v>76247100</v>
       </c>
-      <c r="AM76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP76" s="3">
         <v>82867500</v>
       </c>
-      <c r="AO76" s="3" t="s">
+      <c r="AQ76" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8304,132 +8680,144 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8475,80 +8863,86 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T81" s="3">
         <v>4090200</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V81" s="3">
         <v>3469100</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X81" s="3">
         <v>4126200</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z81" s="3">
         <v>1644700</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB81" s="3">
         <v>1460700</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD81" s="3">
         <v>1642500</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF81" s="3">
         <v>2584600</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH81" s="3">
         <v>-947500</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>2941500</v>
       </c>
-      <c r="AI81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL81" s="3">
         <v>3174100</v>
       </c>
-      <c r="AK81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN81" s="3">
         <v>3535400</v>
       </c>
-      <c r="AM81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP81" s="3">
         <v>2928700</v>
       </c>
-      <c r="AO81" s="3" t="s">
+      <c r="AQ81" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8590,127 +8984,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-224900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>-207000</v>
+      </c>
+      <c r="F83" s="3">
         <v>-107200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>-115400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>-190200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>-191500</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3">
         <v>-163200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>-162400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>-248500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>-228000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>-177700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>-188800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>217200</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V83" s="3">
         <v>943200</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z83" s="3">
         <v>1172900</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD83" s="3">
         <v>699300</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF83" s="3">
         <v>914100</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH83" s="3">
         <v>781900</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>206400</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL83" s="3">
         <v>222200</v>
       </c>
-      <c r="AK83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN83" s="3">
         <v>261400</v>
       </c>
-      <c r="AM83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP83" s="3">
         <v>342800</v>
       </c>
-      <c r="AO83" s="3" t="s">
+      <c r="AQ83" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8828,8 +9230,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8947,8 +9355,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9066,8 +9480,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9185,8 +9605,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9304,127 +9730,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4545900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>4587800</v>
+      </c>
+      <c r="F89" s="3">
         <v>4087100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>4084200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>9223700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>8489000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2726000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2936600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>3542300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>3566700</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P89" s="3">
         <v>2299100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2288100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>2868400</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V89" s="3">
         <v>10772700</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z89" s="3">
         <v>22574200</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD89" s="3">
         <v>4499200</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF89" s="3">
         <v>4792700</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH89" s="3">
         <v>1097700</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>7363200</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL89" s="3">
         <v>5685100</v>
       </c>
-      <c r="AK89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN89" s="3">
         <v>12855800</v>
       </c>
-      <c r="AM89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP89" s="3">
         <v>5218800</v>
       </c>
-      <c r="AO89" s="3" t="s">
+      <c r="AQ89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9466,127 +9904,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-99400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-100300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-143800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-143700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-107500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-98900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-149100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-160600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-100700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-101400</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P91" s="3">
         <v>-77500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-77100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-148000</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-264000</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-125000</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-388000</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-315200</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-225900</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-169200</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-350300</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-207600</v>
       </c>
-      <c r="AK91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN91" s="3">
         <v>-233400</v>
       </c>
-      <c r="AM91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP91" s="3">
         <v>328700</v>
       </c>
-      <c r="AO91" s="3" t="s">
+      <c r="AQ91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9704,8 +10150,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9823,127 +10275,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2319200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2340600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2863100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-2861100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-3564900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-3280900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-3557800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-3832800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2344400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-2360600</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P94" s="3">
         <v>72600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>72300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-889200</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V94" s="3">
         <v>-9703800</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-11401300</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-4910100</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-7598400</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-9962400</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>6915200</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-8020000</v>
       </c>
-      <c r="AK94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN94" s="3">
         <v>-5822000</v>
       </c>
-      <c r="AM94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP94" s="3">
         <v>-11123000</v>
       </c>
-      <c r="AO94" s="3" t="s">
+      <c r="AQ94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9985,127 +10449,135 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2855000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>2881400</v>
+      </c>
+      <c r="F96" s="3">
         <v>113300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>113200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>2810300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>2586500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>93200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>100400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>2453100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>2470100</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3">
         <v>2149600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>2139300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>58800</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-3782400</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-1738500</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>209000</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-4055100</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-107600</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-3648700</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-168300</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-3307600</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-99800</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AQ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10223,8 +10695,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10342,8 +10820,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10461,361 +10945,385 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4524200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-4565900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2302500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-2300800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2978300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2741000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-776000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-835900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-3126500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-3148100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P100" s="3">
         <v>-2556200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-2544000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-627900</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V100" s="3">
         <v>-4697400</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-4914200</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-2034800</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-6157300</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-1335500</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>5542700</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL100" s="3">
         <v>-1286900</v>
       </c>
-      <c r="AK100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN100" s="3">
         <v>-5569600</v>
       </c>
-      <c r="AM100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP100" s="3">
         <v>-1423800</v>
       </c>
-      <c r="AO100" s="3" t="s">
+      <c r="AQ100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-525000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-483100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-122700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-132200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>277000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>278900</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3">
         <v>49700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>49400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-125600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-115200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-119700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-127200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T101" s="3">
+      <c r="T101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V101" s="3">
         <v>219000</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X101" s="3">
+      <c r="X101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-735100</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AB101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD101" s="3">
         <v>387600</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF101" s="3">
         <v>163500</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH101" s="3">
         <v>338300</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>1832600</v>
       </c>
-      <c r="AI101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL101" s="3">
         <v>495900</v>
       </c>
-      <c r="AK101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN101" s="3">
         <v>-1042300</v>
       </c>
-      <c r="AM101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP101" s="3">
         <v>-204200</v>
       </c>
-      <c r="AO101" s="3" t="s">
+      <c r="AQ101" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1742300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1758300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-477300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-476900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>2155600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1983900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1730500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1864300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1651700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1663100</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-134800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-134200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1225800</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V102" s="3">
         <v>-3409500</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z102" s="3">
         <v>5523600</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-1651900</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-9260600</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-9861800</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>21653700</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL102" s="3">
         <v>-3125900</v>
       </c>
-      <c r="AK102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN102" s="3">
         <v>421900</v>
       </c>
-      <c r="AM102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP102" s="3">
         <v>-7532300</v>
       </c>
-      <c r="AO102" s="3" t="s">
+      <c r="AQ102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
